--- a/TruScore logic/BODY Pillar.xlsx
+++ b/TruScore logic/BODY Pillar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TrueScan-FoodScanner\TruScore logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4D754D-2B25-4F9D-81B5-241E177FA29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88306D36-F5DE-4A2F-A001-17CA6E8D6395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{047CDB1A-9F0D-4B6A-BC6F-C5F1664E65A6}"/>
+    <workbookView xWindow="33735" yWindow="750" windowWidth="23055" windowHeight="14730" xr2:uid="{047CDB1A-9F0D-4B6A-BC6F-C5F1664E65A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,9 +102,6 @@
     <t xml:space="preserve"> nova_group (number 1-4) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Base adj: 1=+3, 2=0 (no adjustment), 3=-3, 4=-8 (cap -10 total processing penalties) </t>
-  </si>
-  <si>
     <t xml:space="preserve"> S\'e3o Paulo quant: meta-2025 studies show obesity drop 20% for 1. Ties expertise; cap for fairness. Local confirms boost accuracy. </t>
   </si>
   <si>
@@ -141,9 +138,6 @@
     <t xml:space="preserve"> nutriscore_grade (string a-e) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Base 15 + adjustment: A equiv=+10 (total 25), B=+5 (20), C=0 (15), D=-5 (10), E=-10 (5). </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Official EU Nutri-Score (G20 adopted); Sant\'e9 Publique studies: A cuts CVD 20% vs E. Caps prevent extremes. Local govt geo-mappings de-scoped for MVP\'97stick to OFF for speed/simplicity. </t>
   </si>
   <si>
@@ -166,6 +160,12 @@
   </si>
   <si>
     <t xml:space="preserve"> 1. Country OFF tags/OBF/OPROD &gt; 2. Global OFF &gt; 3. EWG/WHO if prior missing; deduct on unique matching risks (dedup tags). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Base 15 + adjustment: A equiv=+7 (total 22), B=+3 (18), C=0 (15), D=-3 (12), E=-7 (8). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Base adj: 1=+3, 2=+1, 3=-1, 4=-6 (cap -10 total processing penalties) </t>
   </si>
 </sst>
 </file>
@@ -227,11 +227,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +562,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -591,7 +591,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -620,7 +620,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
@@ -628,26 +628,26 @@
         <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
@@ -655,7 +655,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>23</v>
@@ -664,46 +664,46 @@
         <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="176.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
+      <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
@@ -712,19 +712,19 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
